--- a/banking_application_forms/036_credit_card_application_form--banking_application_forms.xlsx
+++ b/banking_application_forms/036_credit_card_application_form--banking_application_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'employed',_'value':_'employed'}</t>
+          <t>employed</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Employed', 'value': 'employed'}</t>
+          <t>Employed</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'unemployed',_'value':_'unemployed'}</t>
+          <t>unemployed</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Unemployed', 'value': 'unemployed'}</t>
+          <t>Unemployed</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'retired',_'value':_'retired'}</t>
+          <t>retired</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Retired', 'value': 'retired'}</t>
+          <t>Retired</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'full_time',_'value':_'full_time'}</t>
+          <t>full_time</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Full time', 'value': 'full_time'}</t>
+          <t>Full time</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'part_time',_'value':_'part_time'}</t>
+          <t>part_time</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Part time', 'value': 'part_time'}</t>
+          <t>Part time</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'self_employed',_'value':_'self_employed'}</t>
+          <t>self_employed</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Self employed', 'value': 'self_employed'}</t>
+          <t>Self employed</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'excellent',_'value':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Excellent', 'value': 'excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'good',_'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Good', 'value': 'good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'fair',_'value':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Fair', 'value': 'fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'bad',_'value':_'bad'}</t>
+          <t>bad</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Bad', 'value': 'bad'}</t>
+          <t>Bad</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'master_card',_'value':_'master_card'}</t>
+          <t>master_card</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Master Card', 'value': 'master_card'}</t>
+          <t>Master Card</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'visa',_'value':_'visa'}</t>
+          <t>visa</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Visa', 'value': 'visa'}</t>
+          <t>Visa</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'american_express',_'value':_'american_express'}</t>
+          <t>american_express</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'American Express', 'value': 'american_express'}</t>
+          <t>American Express</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'gold',_'value':_'gold'}</t>
+          <t>gold</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Gold', 'value': 'gold'}</t>
+          <t>Gold</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'silver',_'value':_'silver'}</t>
+          <t>silver</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Silver', 'value': 'silver'}</t>
+          <t>Silver</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'platinum',_'value':_'platinum'}</t>
+          <t>platinum</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Platinum', 'value': 'platinum'}</t>
+          <t>Platinum</t>
         </is>
       </c>
     </row>
